--- a/ds/planejamento/4semestre/planos/Plano_de_Ensino_PPDM2.xlsx
+++ b/ds/planejamento/4semestre/planos/Plano_de_Ensino_PPDM2.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Instrutor\Downloads\planos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Instrutor\Desktop\senai2026\ds\planejamento\4semestre\planos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2254A7-2DDA-4222-BD35-994755FB85B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA3F7B81-B6EB-4A14-BF82-CF97C62D5AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plano de Ensino" sheetId="2" r:id="rId1"/>
     <sheet name="Agrotech" sheetId="6" r:id="rId2"/>
+    <sheet name="ProjetoEntregas" sheetId="9" r:id="rId3"/>
+    <sheet name="Carrinho de compras" sheetId="8" r:id="rId4"/>
+    <sheet name="PapelariaClaroEscuro" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="212">
   <si>
     <t>PLANO DE ENSINO</t>
   </si>
@@ -172,9 +175,6 @@
     <t>Técnico em Desenvolvimento de Sistemas</t>
   </si>
   <si>
-    <t>Programação Para Dispositivos Moveis 1</t>
-  </si>
-  <si>
     <t>Desenvolver capacidades técnicas e socioemocionais que permitem criar aplicativos para dispositivos móveis e fazer sua integração com outras plataformas.</t>
   </si>
   <si>
@@ -229,9 +229,6 @@
   </si>
   <si>
     <t>Docente : Wellington Fábio de O. Martins</t>
-  </si>
-  <si>
-    <t>Data :  21/01/2025</t>
   </si>
   <si>
     <t>Data:   /   /2026</t>
@@ -835,9 +832,6 @@
     <t>Atividade Agrotech</t>
   </si>
   <si>
-    <t>Repositório da API: https://github.com/wellifabio/agro-api-jserver-swagger</t>
-  </si>
-  <si>
     <t>Wireframes</t>
   </si>
   <si>
@@ -848,9 +842,6 @@
   </si>
   <si>
     <t>Como programador de aplicativos para dispositivos móveis, você deve desenvolver um aplicativo para celular atendendo aos requisitos funcionais a seguir.</t>
-  </si>
-  <si>
-    <t>Requisitos funcionais</t>
   </si>
   <si>
     <t>[RF001] Tela de login</t>
@@ -883,7 +874,342 @@
     <t>Ao clicar em um animal específico na lista um modal com os detalhes do animal deve ser exibido, pemitindo a edição ou exclusão do mesmo.</t>
   </si>
   <si>
-    <t>O espaço para fotos pode ser editado abrindo a câmera do celular para fotografar o animal</t>
+    <t>Programação Para Dispositivos Moveis 2</t>
+  </si>
+  <si>
+    <t>Data :  23/07/2026</t>
+  </si>
+  <si>
+    <t>Requisitos funcionais:</t>
+  </si>
+  <si>
+    <t>Acrescente um botão flutuante no final da página (+) para abrir um modal com um formulário para adicionar animais.</t>
+  </si>
+  <si>
+    <t>Ao clicar na foto do animal no modal de detalhes, abra a câmera para tirar uma foto e envie para a API alterando o campo imagem</t>
+  </si>
+  <si>
+    <t>Acrescente a funcionalidade de enviar dados para a API ao clicar no botão cadastrar, enviando também o token para validação</t>
+  </si>
+  <si>
+    <t>Ao clicar no botão salvar os dados alterados devem ser enviados juntamente com o token.</t>
+  </si>
+  <si>
+    <t>https://github.com/wellifabio/agro-api-jserver-swagger</t>
+  </si>
+  <si>
+    <t>Repositório da API</t>
+  </si>
+  <si>
+    <t>Acesse o link do repositório da API, clone eo repositório e siga as instruções em README.md para executar e testar</t>
+  </si>
+  <si>
+    <t>Exemplo de Listas Cores e Temas</t>
+  </si>
+  <si>
+    <t>Exemplo de um App com listas de produtos de uma papelaria</t>
+  </si>
+  <si>
+    <t>Funcionalidades</t>
+  </si>
+  <si>
+    <t>Recursos</t>
+  </si>
+  <si>
+    <t>Navegação entre telas</t>
+  </si>
+  <si>
+    <t>Navigator.push()</t>
+  </si>
+  <si>
+    <t>Navigator.pop()</t>
+  </si>
+  <si>
+    <t>Imagens locais e da web</t>
+  </si>
+  <si>
+    <t>Image.asset()</t>
+  </si>
+  <si>
+    <t>Image.network()</t>
+  </si>
+  <si>
+    <t>Consumir dados de api</t>
+  </si>
+  <si>
+    <t>http.get(), http: ^1.1.0</t>
+  </si>
+  <si>
+    <t>Converter dados em lista dinamica</t>
+  </si>
+  <si>
+    <t>json.decode(dados)</t>
+  </si>
+  <si>
+    <t>Criar Listas</t>
+  </si>
+  <si>
+    <t>ListView.builder()</t>
+  </si>
+  <si>
+    <t>Arquivo de temas escuro e claro</t>
+  </si>
+  <si>
+    <t>ThemeData.light().copyWith()</t>
+  </si>
+  <si>
+    <t>ThemeData.dark().copyWith()</t>
+  </si>
+  <si>
+    <t>Tecnologias</t>
+  </si>
+  <si>
+    <t>Flutter</t>
+  </si>
+  <si>
+    <t>VsCode</t>
+  </si>
+  <si>
+    <t>Android Studio</t>
+  </si>
+  <si>
+    <t>Screenshots</t>
+  </si>
+  <si>
+    <t>Outras informações</t>
+  </si>
+  <si>
+    <t>Comando para gerar o .apk para instalar no celr com Android e testar</t>
+  </si>
+  <si>
+    <t>flutter build apk --release</t>
+  </si>
+  <si>
+    <r>
+      <t>As imagens .network geralmente não aparecem quando instalamos o .apk no dispositivo, para corrigir temos que adicionar a permição no arquivo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>AndroidManifest.xml</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> que fica localizado em android/app/src/main antes de gerar o .apk</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0550AE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>uses-permission</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6639BA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>android:name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0A3069"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"android.permission.INTERNET"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>/&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>Atividade</t>
+  </si>
+  <si>
+    <t>Clone e execute este App no seu PC</t>
+  </si>
+  <si>
+    <t>Estude os codigos em lib e pubspec.yaml</t>
+  </si>
+  <si>
+    <t>Crie uma lista tipo json tipo mockup com outros produtos</t>
+  </si>
+  <si>
+    <t>Coloque esta lista em um repositório público gitub</t>
+  </si>
+  <si>
+    <t>Crie um App que renderiza a lista de produtos, com as telas SlashScreen com animação em um ícone, Login e lista, ao clicar em um item da lista exiba os detalhes em um modal.</t>
+  </si>
+  <si>
+    <t>Acrescente a funcionalidade de troca de tema claro e escuro</t>
+  </si>
+  <si>
+    <t>Screenshots ------------------------------------------------&gt;</t>
+  </si>
+  <si>
+    <t>Entrega de pedidos de restaurante</t>
+  </si>
+  <si>
+    <t>Atividade NossoFood</t>
+  </si>
+  <si>
+    <t>Diversos estabelecimentos comerciais de nossa região utilizam o Ifood, 99 Food entre outros aplicativos de entrega, porém muitos estabelecimentos preferem um aplicativo próprio, pensando nisso vamos desenvolver um modelo</t>
+  </si>
+  <si>
+    <t>Enviar os dados via POST para a API que devolve sucesso ou fracasso do login</t>
+  </si>
+  <si>
+    <t>Se os dados de acesso estiverem corretos e validados pela API, a mesma retorna os dados do usuário e o aplicativo direciona para a tela de pedidos</t>
+  </si>
+  <si>
+    <t>Como programador de aplicativos para dispositivos móveis, você deve desenvolver um aplicativo para celular para o entregador fazer login e verificar seus pedidos atendendo aos requisitos funcionais a seguir.</t>
+  </si>
+  <si>
+    <t>[RF002] Tela Pedidos</t>
+  </si>
+  <si>
+    <t>Listar os pedidos designados para a entrega, somente os pedidos do usuário que está logado</t>
+  </si>
+  <si>
+    <t>Botão &lt;- voltar que deve sair do sistema</t>
+  </si>
+  <si>
+    <t>Cards com os dados básicos de cada pedido, conforme exemplo no wireframe.</t>
+  </si>
+  <si>
+    <t>Botão concluído para informar a conclusão da entrega para a API, deve abrir um modal de confirmação que pede um código ao cliente e informa, somente com o código correto o pedido é concluído e desaparece da lista</t>
+  </si>
+  <si>
+    <t>Ao clicar no card do pedido um modal com detalhes do pedido deve ser aberto contendo:</t>
+  </si>
+  <si>
+    <t>Um botão Mapas, que direciona para a tela de navegação um mapa destacando o endereço de entrega</t>
+  </si>
+  <si>
+    <t>O botão concluir a entrega que direciona para o modal de confirmação</t>
+  </si>
+  <si>
+    <t>Ao entrar na tela deve abrir o mapa marcando o restaurante, o endereço de entrega e traçar um</t>
+  </si>
+  <si>
+    <t>caminho entre estes pontos</t>
+  </si>
+  <si>
+    <t>[RF004] Tela de mapa</t>
+  </si>
+  <si>
+    <t>[RF003] Modal de detalhes</t>
+  </si>
+  <si>
+    <t>Tarefas adicionais</t>
+  </si>
+  <si>
+    <t>Crie uma API com dados de usuários, pedidos por usuário antes de desenvolver o aplicativo</t>
+  </si>
+  <si>
+    <t>Se prferir pode ser um mokup com JSON server</t>
+  </si>
+  <si>
+    <t>Carrinho de compras</t>
+  </si>
+  <si>
+    <t>Exemplo de um carrinho de compras com flutter</t>
+  </si>
+  <si>
+    <t>Imagens da web</t>
+  </si>
+  <si>
+    <t>Loal storage, compartihar dados entre telas</t>
+  </si>
+  <si>
+    <t>shared_preferences: ^2.2.2</t>
+  </si>
+  <si>
+    <t>Criar grid de Containers</t>
+  </si>
+  <si>
+    <t>GridView.builder()</t>
+  </si>
+  <si>
+    <t>Verificar a orientação do celular, vertical ou horizontal</t>
+  </si>
+  <si>
+    <t>MediaQuery.of(context).orientation</t>
+  </si>
+  <si>
+    <t>Filtrar dados</t>
+  </si>
+  <si>
+    <t>Lógica, listas</t>
+  </si>
+  <si>
+    <r>
+      <t>Neste repositório existe um arquivo </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>app-release.apk na pasta assets caso queira testar em seu celular Android, basta fazer download e instalar.</t>
+    </r>
+  </si>
+  <si>
+    <t>Crie uma lista tipo json tipo mockup com produtos e usuários</t>
+  </si>
+  <si>
+    <t>Crie um App de carrinho de compras, com splash, login e carrinho como este porém personalizado com sua lista</t>
+  </si>
+  <si>
+    <t>Ao conluir gere o APK, instale e teste em um celular com Anroid</t>
   </si>
 </sst>
 </file>
@@ -894,11 +1220,18 @@
     <numFmt numFmtId="164" formatCode="dd/mm"/>
     <numFmt numFmtId="165" formatCode="d/m"/>
   </numFmts>
-  <fonts count="40" x14ac:knownFonts="1">
+  <fonts count="56" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1141,8 +1474,110 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16.5"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2328"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0550AE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF6639BA"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0A3069"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1173,8 +1608,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="34">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -1559,326 +2006,257 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD1D9E0"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD1D9E0"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD1D9E0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD1D9E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD1D9E0"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD1D9E0"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD1D9E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD1D9E0"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD1D9E0"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFD1D9E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1893,94 +2271,302 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2309,13 +2895,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>4686300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2348,6 +2934,462 @@
         <a:xfrm>
           <a:off x="0" y="600075"/>
           <a:ext cx="8191500" cy="4638675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>74840</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>92528</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2491429</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>107010</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D797593C-56DB-086A-4865-72E7F6C9A88B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7368269" y="2106385"/>
+          <a:ext cx="2416589" cy="5266839"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>89806</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2560962</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>23939</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3238B629-6023-9E53-5585-F1255EF7B37D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7360104" y="7356020"/>
+          <a:ext cx="2494287" cy="4919790"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2707823</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5134495</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>68035</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagem 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECB69BB1-1B41-8645-981B-D4932B4AF3EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10001252" y="4585608"/>
+          <a:ext cx="2426672" cy="4884963"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>22638</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>31296</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1" descr="Screenshots">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tgtFrame="_blank"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FB97117-1888-B961-23A8-4ED34821A850}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="12134850" y="670338"/>
+          <a:ext cx="7648575" cy="5368512"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2088262</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>258912</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>122465</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>100694</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2" descr="Screenshots">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tgtFrame="_blank"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD0DEF53-1137-DDEF-9112-07620604A190}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6592226" y="6354912"/>
+          <a:ext cx="7423132" cy="5194832"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>243871</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>68034</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>175533</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>32655</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagem 4" descr="Screenshots">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C764C8A0-7DAF-3DF5-9198-C1EFFFFD40CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="14136764" y="6164034"/>
+          <a:ext cx="2653090" cy="5755821"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>53346</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>77807</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1" descr="Screenshots">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tgtFrame="_blank"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97DAC1F2-7831-8513-658B-36A010B3825A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8439149" y="472446"/>
+          <a:ext cx="6810376" cy="4882211"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>137978</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2" descr="Screenshots">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tgtFrame="_blank"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{685245CE-DAFC-27D8-6683-5BCF033E86B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8458200" y="5329103"/>
+          <a:ext cx="6781800" cy="4453072"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2588,134 +3630,134 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="111" t="s">
+      <c r="A3" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="112"/>
-      <c r="C3" s="115" t="s">
+      <c r="B3" s="90"/>
+      <c r="C3" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="116"/>
-      <c r="E3" s="105" t="s">
+      <c r="D3" s="77"/>
+      <c r="E3" s="83" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="84"/>
+      <c r="G3" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="74"/>
+    </row>
+    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="89"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="87" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" s="88"/>
+      <c r="G4" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="106"/>
-      <c r="G3" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="113"/>
-      <c r="I3" s="113" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="113"/>
-    </row>
-    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="111"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="109" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="110"/>
-      <c r="G4" s="94" t="s">
-        <v>63</v>
-      </c>
-      <c r="H4" s="94"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="91"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="91" t="s">
+      <c r="B5" s="95"/>
+      <c r="C5" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" s="80"/>
+      <c r="E5" s="140" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="141"/>
+      <c r="G5" s="73" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+    </row>
+    <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="95"/>
+      <c r="B6" s="96"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="81" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="82"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+    </row>
+    <row r="7" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="94" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="95"/>
+      <c r="C7" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="91"/>
-      <c r="E5" s="101" t="s">
+      <c r="D7" s="97"/>
+      <c r="E7" s="85" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="102"/>
-      <c r="G5" s="94" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
-    </row>
-    <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="80"/>
-      <c r="B6" s="79"/>
-      <c r="C6" s="91"/>
-      <c r="D6" s="91"/>
-      <c r="E6" s="103" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="104"/>
-      <c r="G6" s="91"/>
-      <c r="H6" s="91"/>
-      <c r="I6" s="91"/>
-      <c r="J6" s="91"/>
-    </row>
-    <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="97" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="80"/>
-      <c r="C7" s="98" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="98"/>
-      <c r="E7" s="107" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="108"/>
-      <c r="G7" s="91"/>
-      <c r="H7" s="91"/>
-      <c r="I7" s="91"/>
-      <c r="J7" s="91"/>
-    </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="80"/>
-      <c r="B8" s="79"/>
-      <c r="C8" s="98"/>
-      <c r="D8" s="98"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="91"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="91"/>
-      <c r="J8" s="91"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+    </row>
+    <row r="8" spans="1:27" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="95"/>
+      <c r="B8" s="96"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
     </row>
     <row r="9" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="99" t="s">
+      <c r="A9" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="99"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
-      <c r="I9" s="99"/>
-      <c r="J9" s="99"/>
+      <c r="B9" s="98"/>
+      <c r="C9" s="98"/>
+      <c r="D9" s="98"/>
+      <c r="E9" s="98"/>
+      <c r="F9" s="98"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="98"/>
+      <c r="I9" s="98"/>
+      <c r="J9" s="98"/>
     </row>
     <row r="10" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="25" t="s">
@@ -2736,14 +3778,14 @@
       <c r="F10" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="100" t="s">
+      <c r="G10" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="100"/>
-      <c r="I10" s="100" t="s">
+      <c r="H10" s="99"/>
+      <c r="I10" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="100"/>
+      <c r="J10" s="99"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -2764,29 +3806,29 @@
     </row>
     <row r="11" spans="1:27" ht="123" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="28" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B11" s="23">
         <v>12</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="38" t="s">
+      <c r="G11" s="71"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="177" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="43"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="J11" s="44"/>
+      <c r="J11" s="178"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -2807,29 +3849,29 @@
     </row>
     <row r="12" spans="1:27" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2">
         <v>16</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
-      <c r="F12" s="121" t="s">
-        <v>54</v>
+      <c r="F12" s="68" t="s">
+        <v>53</v>
       </c>
-      <c r="G12" s="43"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="95" t="s">
-        <v>64</v>
+      <c r="G12" s="71"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="179" t="s">
+        <v>62</v>
       </c>
-      <c r="J12" s="96"/>
+      <c r="J12" s="180"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -2850,27 +3892,27 @@
     </row>
     <row r="13" spans="1:27" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="29" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B13" s="2">
         <v>16</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
-      <c r="F13" s="119"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="123" t="s">
-        <v>53</v>
+      <c r="F13" s="69"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="181" t="s">
+        <v>52</v>
       </c>
-      <c r="J13" s="124"/>
+      <c r="J13" s="182"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -2891,25 +3933,25 @@
     </row>
     <row r="14" spans="1:27" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A14" s="28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B14" s="23">
         <v>20</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
-      <c r="F14" s="120"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="125"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="177"/>
+      <c r="J14" s="178"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -2930,29 +3972,29 @@
     </row>
     <row r="15" spans="1:27" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A15" s="29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B15" s="2">
         <v>16</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E15" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="24" t="s">
-        <v>59</v>
+      <c r="G15" s="71"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="179" t="s">
+        <v>62</v>
       </c>
-      <c r="G15" s="43"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="95" t="s">
-        <v>64</v>
-      </c>
-      <c r="J15" s="96"/>
+      <c r="J15" s="180"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -2983,10 +4025,10 @@
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="15"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="42"/>
+      <c r="G16" s="136"/>
+      <c r="H16" s="137"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="139"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -3006,18 +4048,18 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="59" t="s">
+      <c r="A17" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="61"/>
+      <c r="B17" s="118"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="118"/>
+      <c r="J17" s="119"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -3037,18 +4079,18 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="62" t="s">
+      <c r="A18" s="120" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
+      <c r="B18" s="120"/>
+      <c r="C18" s="120"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="120"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="120"/>
+      <c r="J18" s="120"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -3068,18 +4110,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="56" t="s">
-        <v>81</v>
+      <c r="A19" s="116" t="s">
+        <v>79</v>
       </c>
-      <c r="B19" s="56"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="56"/>
+      <c r="B19" s="116"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="116"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="116"/>
+      <c r="I19" s="116"/>
+      <c r="J19" s="116"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -3099,18 +4141,18 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="62" t="s">
+      <c r="A20" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
+      <c r="B20" s="120"/>
+      <c r="C20" s="120"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="120"/>
+      <c r="J20" s="120"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -3130,18 +4172,18 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="176.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="56" t="s">
-        <v>82</v>
+      <c r="A21" s="116" t="s">
+        <v>80</v>
       </c>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="56"/>
+      <c r="B21" s="116"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="116"/>
+      <c r="E21" s="116"/>
+      <c r="F21" s="116"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="116"/>
+      <c r="I21" s="116"/>
+      <c r="J21" s="116"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -3158,18 +4200,18 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="129" t="s">
-        <v>84</v>
+      <c r="A22" s="60" t="s">
+        <v>82</v>
       </c>
-      <c r="B22" s="130"/>
-      <c r="C22" s="130"/>
-      <c r="D22" s="130"/>
-      <c r="E22" s="130"/>
-      <c r="F22" s="130"/>
-      <c r="G22" s="127"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="127"/>
-      <c r="J22" s="128"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="59"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -3186,18 +4228,18 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="129" t="s">
-        <v>85</v>
+      <c r="A23" s="60" t="s">
+        <v>83</v>
       </c>
-      <c r="B23" s="130"/>
-      <c r="C23" s="130"/>
-      <c r="D23" s="130"/>
-      <c r="E23" s="127"/>
-      <c r="F23" s="127"/>
-      <c r="G23" s="127"/>
-      <c r="H23" s="127"/>
-      <c r="I23" s="127"/>
-      <c r="J23" s="128"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="59"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -3214,18 +4256,18 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="126"/>
-      <c r="B24" s="127"/>
-      <c r="C24" s="127"/>
-      <c r="D24" s="127"/>
-      <c r="E24" s="127"/>
-      <c r="F24" s="127"/>
-      <c r="G24" s="130" t="s">
-        <v>86</v>
+      <c r="A24" s="57"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="61" t="s">
+        <v>84</v>
       </c>
-      <c r="H24" s="130"/>
-      <c r="I24" s="130"/>
-      <c r="J24" s="131"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="62"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -3242,18 +4284,18 @@
       <c r="AA24" s="1"/>
     </row>
     <row r="25" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="129" t="s">
-        <v>83</v>
+      <c r="A25" s="60" t="s">
+        <v>81</v>
       </c>
-      <c r="B25" s="130"/>
-      <c r="C25" s="130"/>
-      <c r="D25" s="130"/>
-      <c r="E25" s="130"/>
-      <c r="F25" s="130"/>
-      <c r="G25" s="127"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="127"/>
-      <c r="J25" s="128"/>
+      <c r="B25" s="61"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="59"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -3270,18 +4312,18 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="126"/>
-      <c r="B26" s="127"/>
-      <c r="C26" s="128"/>
-      <c r="D26" s="129" t="s">
-        <v>106</v>
+      <c r="A26" s="57"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="60" t="s">
+        <v>104</v>
       </c>
-      <c r="E26" s="130"/>
-      <c r="F26" s="130"/>
-      <c r="G26" s="130"/>
-      <c r="H26" s="130"/>
-      <c r="I26" s="130"/>
-      <c r="J26" s="131"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="62"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -3298,18 +4340,18 @@
       <c r="AA26" s="1"/>
     </row>
     <row r="27" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="62" t="s">
+      <c r="A27" s="120" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
+      <c r="B27" s="120"/>
+      <c r="C27" s="120"/>
+      <c r="D27" s="120"/>
+      <c r="E27" s="120"/>
+      <c r="F27" s="120"/>
+      <c r="G27" s="120"/>
+      <c r="H27" s="120"/>
+      <c r="I27" s="120"/>
+      <c r="J27" s="120"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -3329,18 +4371,18 @@
       <c r="AA27" s="1"/>
     </row>
     <row r="28" spans="1:27" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="56" t="s">
-        <v>87</v>
+      <c r="A28" s="116" t="s">
+        <v>85</v>
       </c>
-      <c r="B28" s="56"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
+      <c r="B28" s="116"/>
+      <c r="C28" s="116"/>
+      <c r="D28" s="116"/>
+      <c r="E28" s="116"/>
+      <c r="F28" s="116"/>
+      <c r="G28" s="116"/>
+      <c r="H28" s="116"/>
+      <c r="I28" s="116"/>
+      <c r="J28" s="116"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -3360,16 +4402,16 @@
       <c r="AA28" s="1"/>
     </row>
     <row r="29" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A29" s="66"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="67"/>
-      <c r="F29" s="67"/>
-      <c r="G29" s="67"/>
-      <c r="H29" s="67"/>
-      <c r="I29" s="67"/>
-      <c r="J29" s="68"/>
+      <c r="A29" s="124"/>
+      <c r="B29" s="125"/>
+      <c r="C29" s="125"/>
+      <c r="D29" s="125"/>
+      <c r="E29" s="125"/>
+      <c r="F29" s="125"/>
+      <c r="G29" s="125"/>
+      <c r="H29" s="125"/>
+      <c r="I29" s="125"/>
+      <c r="J29" s="126"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -3389,16 +4431,16 @@
       <c r="AA29" s="1"/>
     </row>
     <row r="30" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="69"/>
-      <c r="B30" s="70"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="71"/>
+      <c r="A30" s="127"/>
+      <c r="B30" s="128"/>
+      <c r="C30" s="128"/>
+      <c r="D30" s="128"/>
+      <c r="E30" s="128"/>
+      <c r="F30" s="128"/>
+      <c r="G30" s="128"/>
+      <c r="H30" s="128"/>
+      <c r="I30" s="128"/>
+      <c r="J30" s="129"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -3418,18 +4460,18 @@
       <c r="AA30" s="1"/>
     </row>
     <row r="31" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="92" t="s">
+      <c r="A31" s="91" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="92"/>
-      <c r="C31" s="92"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="92"/>
-      <c r="F31" s="92"/>
-      <c r="G31" s="92"/>
-      <c r="H31" s="92"/>
-      <c r="I31" s="92"/>
-      <c r="J31" s="92"/>
+      <c r="B31" s="91"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="91"/>
+      <c r="E31" s="91"/>
+      <c r="F31" s="91"/>
+      <c r="G31" s="91"/>
+      <c r="H31" s="91"/>
+      <c r="I31" s="91"/>
+      <c r="J31" s="91"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -3449,22 +4491,22 @@
       <c r="AA31" s="1"/>
     </row>
     <row r="32" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="63" t="s">
+      <c r="A32" s="121" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="64"/>
-      <c r="C32" s="64"/>
-      <c r="D32" s="65" t="s">
+      <c r="B32" s="122"/>
+      <c r="C32" s="122"/>
+      <c r="D32" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="65"/>
-      <c r="F32" s="65"/>
-      <c r="G32" s="93" t="s">
+      <c r="E32" s="123"/>
+      <c r="F32" s="123"/>
+      <c r="G32" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="93"/>
+      <c r="J32" s="93"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -3484,12 +4526,12 @@
       <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="64"/>
-      <c r="B33" s="64"/>
-      <c r="C33" s="64"/>
-      <c r="D33" s="65"/>
-      <c r="E33" s="65"/>
-      <c r="F33" s="65"/>
+      <c r="A33" s="122"/>
+      <c r="B33" s="122"/>
+      <c r="C33" s="122"/>
+      <c r="D33" s="123"/>
+      <c r="E33" s="123"/>
+      <c r="F33" s="123"/>
       <c r="G33" s="21">
         <v>1</v>
       </c>
@@ -3521,18 +4563,18 @@
       <c r="AA33" s="1"/>
     </row>
     <row r="34" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="84" t="s">
+      <c r="A34" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="87" t="s">
-        <v>74</v>
+      <c r="B34" s="63" t="s">
+        <v>72</v>
       </c>
-      <c r="C34" s="88"/>
-      <c r="D34" s="134" t="s">
-        <v>99</v>
+      <c r="C34" s="64"/>
+      <c r="D34" s="42" t="s">
+        <v>97</v>
       </c>
-      <c r="E34" s="139"/>
-      <c r="F34" s="140"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="44"/>
       <c r="G34" s="7"/>
       <c r="H34" s="18"/>
       <c r="I34" s="19"/>
@@ -3556,14 +4598,14 @@
       <c r="AA34" s="1"/>
     </row>
     <row r="35" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="122"/>
-      <c r="B35" s="132"/>
-      <c r="C35" s="133"/>
-      <c r="D35" s="141" t="s">
-        <v>100</v>
+      <c r="A35" s="111"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="65" t="s">
+        <v>98</v>
       </c>
-      <c r="E35" s="142"/>
-      <c r="F35" s="143"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="67"/>
       <c r="G35" s="7"/>
       <c r="H35" s="18"/>
       <c r="I35" s="19"/>
@@ -3587,16 +4629,16 @@
       <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="122"/>
-      <c r="B36" s="87" t="s">
-        <v>88</v>
+      <c r="A36" s="111"/>
+      <c r="B36" s="63" t="s">
+        <v>86</v>
       </c>
-      <c r="C36" s="88"/>
-      <c r="D36" s="134" t="s">
-        <v>101</v>
+      <c r="C36" s="64"/>
+      <c r="D36" s="42" t="s">
+        <v>99</v>
       </c>
-      <c r="E36" s="139"/>
-      <c r="F36" s="140"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="44"/>
       <c r="G36" s="7"/>
       <c r="H36" s="18"/>
       <c r="I36" s="19"/>
@@ -3620,14 +4662,14 @@
       <c r="AA36" s="1"/>
     </row>
     <row r="37" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="85"/>
-      <c r="B37" s="132"/>
-      <c r="C37" s="133"/>
-      <c r="D37" s="141" t="s">
-        <v>102</v>
+      <c r="A37" s="112"/>
+      <c r="B37" s="51"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="65" t="s">
+        <v>100</v>
       </c>
-      <c r="E37" s="142"/>
-      <c r="F37" s="143"/>
+      <c r="E37" s="66"/>
+      <c r="F37" s="67"/>
       <c r="G37" s="7"/>
       <c r="H37" s="18"/>
       <c r="I37" s="14"/>
@@ -3651,16 +4693,16 @@
       <c r="AA37" s="1"/>
     </row>
     <row r="38" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="85"/>
-      <c r="B38" s="87" t="s">
-        <v>57</v>
+      <c r="A38" s="112"/>
+      <c r="B38" s="63" t="s">
+        <v>56</v>
       </c>
-      <c r="C38" s="88"/>
-      <c r="D38" s="134" t="s">
-        <v>103</v>
+      <c r="C38" s="64"/>
+      <c r="D38" s="42" t="s">
+        <v>101</v>
       </c>
-      <c r="E38" s="139"/>
-      <c r="F38" s="140"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="44"/>
       <c r="G38" s="7"/>
       <c r="H38" s="18"/>
       <c r="I38" s="14"/>
@@ -3684,14 +4726,14 @@
       <c r="AA38" s="1"/>
     </row>
     <row r="39" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="85"/>
-      <c r="B39" s="89"/>
-      <c r="C39" s="90"/>
-      <c r="D39" s="141" t="s">
-        <v>104</v>
+      <c r="A39" s="112"/>
+      <c r="B39" s="47"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="65" t="s">
+        <v>102</v>
       </c>
-      <c r="E39" s="142"/>
-      <c r="F39" s="143"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="67"/>
       <c r="G39" s="7"/>
       <c r="H39" s="18"/>
       <c r="I39" s="14"/>
@@ -3715,16 +4757,16 @@
       <c r="AA39" s="1"/>
     </row>
     <row r="40" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="85"/>
-      <c r="B40" s="135" t="s">
-        <v>77</v>
+      <c r="A40" s="112"/>
+      <c r="B40" s="45" t="s">
+        <v>75</v>
       </c>
-      <c r="C40" s="136"/>
-      <c r="D40" s="134" t="s">
-        <v>105</v>
+      <c r="C40" s="46"/>
+      <c r="D40" s="42" t="s">
+        <v>103</v>
       </c>
-      <c r="E40" s="139"/>
-      <c r="F40" s="140"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="44"/>
       <c r="G40" s="7"/>
       <c r="H40" s="18"/>
       <c r="I40" s="14"/>
@@ -3748,14 +4790,14 @@
       <c r="AA40" s="1"/>
     </row>
     <row r="41" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="85"/>
-      <c r="B41" s="89"/>
-      <c r="C41" s="90"/>
-      <c r="D41" s="141" t="s">
-        <v>107</v>
+      <c r="A41" s="112"/>
+      <c r="B41" s="47"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="65" t="s">
+        <v>105</v>
       </c>
-      <c r="E41" s="142"/>
-      <c r="F41" s="143"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="67"/>
       <c r="G41" s="7"/>
       <c r="H41" s="18"/>
       <c r="I41" s="14"/>
@@ -3779,16 +4821,16 @@
       <c r="AA41" s="1"/>
     </row>
     <row r="42" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="85"/>
-      <c r="B42" s="135" t="s">
-        <v>89</v>
+      <c r="A42" s="112"/>
+      <c r="B42" s="45" t="s">
+        <v>87</v>
       </c>
-      <c r="C42" s="136"/>
-      <c r="D42" s="134" t="s">
-        <v>108</v>
+      <c r="C42" s="46"/>
+      <c r="D42" s="42" t="s">
+        <v>106</v>
       </c>
-      <c r="E42" s="139"/>
-      <c r="F42" s="140"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
       <c r="G42" s="7"/>
       <c r="H42" s="18"/>
       <c r="I42" s="14"/>
@@ -3812,14 +4854,14 @@
       <c r="AA42" s="1"/>
     </row>
     <row r="43" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="85"/>
-      <c r="B43" s="89"/>
-      <c r="C43" s="90"/>
-      <c r="D43" s="141" t="s">
-        <v>109</v>
+      <c r="A43" s="112"/>
+      <c r="B43" s="47"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="65" t="s">
+        <v>107</v>
       </c>
-      <c r="E43" s="142"/>
-      <c r="F43" s="143"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="67"/>
       <c r="G43" s="7"/>
       <c r="H43" s="18"/>
       <c r="I43" s="14"/>
@@ -3843,16 +4885,16 @@
       <c r="AA43" s="1"/>
     </row>
     <row r="44" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="85"/>
-      <c r="B44" s="137" t="s">
-        <v>56</v>
+      <c r="A44" s="112"/>
+      <c r="B44" s="49" t="s">
+        <v>55</v>
       </c>
-      <c r="C44" s="138"/>
-      <c r="D44" s="134" t="s">
-        <v>110</v>
+      <c r="C44" s="50"/>
+      <c r="D44" s="42" t="s">
+        <v>108</v>
       </c>
-      <c r="E44" s="139"/>
-      <c r="F44" s="140"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="44"/>
       <c r="G44" s="7"/>
       <c r="H44" s="18"/>
       <c r="I44" s="14"/>
@@ -3876,14 +4918,14 @@
       <c r="AA44" s="1"/>
     </row>
     <row r="45" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="86"/>
-      <c r="B45" s="132"/>
-      <c r="C45" s="133"/>
-      <c r="D45" s="141" t="s">
-        <v>111</v>
+      <c r="A45" s="113"/>
+      <c r="B45" s="51"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="65" t="s">
+        <v>109</v>
       </c>
-      <c r="E45" s="142"/>
-      <c r="F45" s="143"/>
+      <c r="E45" s="66"/>
+      <c r="F45" s="67"/>
       <c r="G45" s="7"/>
       <c r="H45" s="18"/>
       <c r="I45" s="14"/>
@@ -3907,18 +4949,18 @@
       <c r="AA45" s="1"/>
     </row>
     <row r="46" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="81" t="s">
+      <c r="A46" s="105" t="s">
         <v>30</v>
       </c>
-      <c r="B46" s="57" t="s">
+      <c r="B46" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="C46" s="58"/>
-      <c r="D46" s="141" t="s">
-        <v>112</v>
+      <c r="C46" s="109"/>
+      <c r="D46" s="65" t="s">
+        <v>110</v>
       </c>
-      <c r="E46" s="142"/>
-      <c r="F46" s="143"/>
+      <c r="E46" s="66"/>
+      <c r="F46" s="67"/>
       <c r="G46" s="7"/>
       <c r="H46" s="18"/>
       <c r="I46" s="14"/>
@@ -3942,16 +4984,16 @@
       <c r="AA46" s="1"/>
     </row>
     <row r="47" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="82"/>
-      <c r="B47" s="57" t="s">
-        <v>60</v>
+      <c r="A47" s="106"/>
+      <c r="B47" s="108" t="s">
+        <v>59</v>
       </c>
-      <c r="C47" s="58"/>
-      <c r="D47" s="141" t="s">
-        <v>113</v>
+      <c r="C47" s="109"/>
+      <c r="D47" s="65" t="s">
+        <v>111</v>
       </c>
-      <c r="E47" s="142"/>
-      <c r="F47" s="143"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="67"/>
       <c r="G47" s="7"/>
       <c r="H47" s="18"/>
       <c r="I47" s="14"/>
@@ -3975,16 +5017,16 @@
       <c r="AA47" s="1"/>
     </row>
     <row r="48" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="82"/>
-      <c r="B48" s="57" t="s">
+      <c r="A48" s="106"/>
+      <c r="B48" s="108" t="s">
         <v>42</v>
       </c>
-      <c r="C48" s="58"/>
-      <c r="D48" s="141" t="s">
-        <v>114</v>
+      <c r="C48" s="109"/>
+      <c r="D48" s="65" t="s">
+        <v>112</v>
       </c>
-      <c r="E48" s="142"/>
-      <c r="F48" s="143"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="67"/>
       <c r="G48" s="7"/>
       <c r="H48" s="18"/>
       <c r="I48" s="14"/>
@@ -4008,16 +5050,16 @@
       <c r="AA48" s="1"/>
     </row>
     <row r="49" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="83"/>
-      <c r="B49" s="57" t="s">
+      <c r="A49" s="107"/>
+      <c r="B49" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="58"/>
-      <c r="D49" s="141" t="s">
-        <v>115</v>
+      <c r="C49" s="109"/>
+      <c r="D49" s="65" t="s">
+        <v>113</v>
       </c>
-      <c r="E49" s="142"/>
-      <c r="F49" s="143"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="67"/>
       <c r="G49" s="7"/>
       <c r="H49" s="18"/>
       <c r="I49" s="14"/>
@@ -4041,14 +5083,14 @@
       <c r="AA49" s="1"/>
     </row>
     <row r="50" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="78"/>
-      <c r="B50" s="78"/>
-      <c r="C50" s="78"/>
-      <c r="D50" s="78"/>
-      <c r="E50" s="78"/>
-      <c r="F50" s="78"/>
-      <c r="G50" s="78"/>
-      <c r="H50" s="78"/>
+      <c r="A50" s="104"/>
+      <c r="B50" s="104"/>
+      <c r="C50" s="104"/>
+      <c r="D50" s="104"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="104"/>
+      <c r="G50" s="104"/>
+      <c r="H50" s="104"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -4070,18 +5112,18 @@
       <c r="AA50" s="1"/>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A51" s="74" t="s">
+      <c r="A51" s="100" t="s">
         <v>13</v>
       </c>
-      <c r="B51" s="75"/>
-      <c r="C51" s="75"/>
-      <c r="D51" s="75"/>
-      <c r="E51" s="76"/>
-      <c r="F51" s="77" t="s">
+      <c r="B51" s="101"/>
+      <c r="C51" s="101"/>
+      <c r="D51" s="101"/>
+      <c r="E51" s="102"/>
+      <c r="F51" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="G51" s="75"/>
-      <c r="H51" s="76"/>
+      <c r="G51" s="101"/>
+      <c r="H51" s="102"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -4106,17 +5148,17 @@
       <c r="A52" s="8">
         <v>12</v>
       </c>
-      <c r="B52" s="46" t="s">
+      <c r="B52" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="47"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="48"/>
-      <c r="F52" s="49">
+      <c r="C52" s="54"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="56">
         <v>100</v>
       </c>
-      <c r="G52" s="47"/>
-      <c r="H52" s="48"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="55"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -4141,17 +5183,17 @@
       <c r="A53" s="8">
         <v>11</v>
       </c>
-      <c r="B53" s="73" t="s">
-        <v>98</v>
+      <c r="B53" s="53" t="s">
+        <v>96</v>
       </c>
-      <c r="C53" s="47"/>
-      <c r="D53" s="47"/>
-      <c r="E53" s="48"/>
-      <c r="F53" s="49">
+      <c r="C53" s="54"/>
+      <c r="D53" s="54"/>
+      <c r="E53" s="55"/>
+      <c r="F53" s="56">
         <v>95</v>
       </c>
-      <c r="G53" s="47"/>
-      <c r="H53" s="48"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="55"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -4176,17 +5218,17 @@
       <c r="A54" s="8">
         <v>10</v>
       </c>
-      <c r="B54" s="73" t="s">
-        <v>97</v>
+      <c r="B54" s="53" t="s">
+        <v>95</v>
       </c>
-      <c r="C54" s="47"/>
-      <c r="D54" s="47"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="49">
+      <c r="C54" s="54"/>
+      <c r="D54" s="54"/>
+      <c r="E54" s="55"/>
+      <c r="F54" s="56">
         <v>90</v>
       </c>
-      <c r="G54" s="47"/>
-      <c r="H54" s="48"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="55"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -4211,17 +5253,17 @@
       <c r="A55" s="8">
         <v>9</v>
       </c>
-      <c r="B55" s="73" t="s">
-        <v>96</v>
+      <c r="B55" s="53" t="s">
+        <v>94</v>
       </c>
-      <c r="C55" s="47"/>
-      <c r="D55" s="47"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="49">
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="55"/>
+      <c r="F55" s="56">
         <v>85</v>
       </c>
-      <c r="G55" s="47"/>
-      <c r="H55" s="48"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="55"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -4246,17 +5288,17 @@
       <c r="A56" s="8">
         <v>8</v>
       </c>
-      <c r="B56" s="73" t="s">
-        <v>95</v>
+      <c r="B56" s="53" t="s">
+        <v>93</v>
       </c>
-      <c r="C56" s="47"/>
-      <c r="D56" s="47"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="49">
+      <c r="C56" s="54"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="55"/>
+      <c r="F56" s="56">
         <v>80</v>
       </c>
-      <c r="G56" s="47"/>
-      <c r="H56" s="48"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="55"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -4281,17 +5323,17 @@
       <c r="A57" s="8">
         <v>7</v>
       </c>
-      <c r="B57" s="73" t="s">
-        <v>94</v>
+      <c r="B57" s="53" t="s">
+        <v>92</v>
       </c>
-      <c r="C57" s="47"/>
-      <c r="D57" s="47"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="49">
+      <c r="C57" s="54"/>
+      <c r="D57" s="54"/>
+      <c r="E57" s="55"/>
+      <c r="F57" s="56">
         <v>75</v>
       </c>
-      <c r="G57" s="47"/>
-      <c r="H57" s="48"/>
+      <c r="G57" s="54"/>
+      <c r="H57" s="55"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
@@ -4316,17 +5358,17 @@
       <c r="A58" s="8">
         <v>6</v>
       </c>
-      <c r="B58" s="73" t="s">
-        <v>93</v>
+      <c r="B58" s="53" t="s">
+        <v>91</v>
       </c>
-      <c r="C58" s="47"/>
-      <c r="D58" s="47"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="49">
+      <c r="C58" s="54"/>
+      <c r="D58" s="54"/>
+      <c r="E58" s="55"/>
+      <c r="F58" s="56">
         <v>70</v>
       </c>
-      <c r="G58" s="47"/>
-      <c r="H58" s="48"/>
+      <c r="G58" s="54"/>
+      <c r="H58" s="55"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
@@ -4351,17 +5393,17 @@
       <c r="A59" s="8">
         <v>5</v>
       </c>
-      <c r="B59" s="73" t="s">
-        <v>92</v>
+      <c r="B59" s="53" t="s">
+        <v>90</v>
       </c>
-      <c r="C59" s="47"/>
-      <c r="D59" s="47"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="49">
+      <c r="C59" s="54"/>
+      <c r="D59" s="54"/>
+      <c r="E59" s="55"/>
+      <c r="F59" s="56">
         <v>65</v>
       </c>
-      <c r="G59" s="47"/>
-      <c r="H59" s="48"/>
+      <c r="G59" s="54"/>
+      <c r="H59" s="55"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
@@ -4386,17 +5428,17 @@
       <c r="A60" s="8">
         <v>4</v>
       </c>
-      <c r="B60" s="73" t="s">
-        <v>91</v>
+      <c r="B60" s="53" t="s">
+        <v>89</v>
       </c>
-      <c r="C60" s="47"/>
-      <c r="D60" s="47"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="49">
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="55"/>
+      <c r="F60" s="56">
         <v>60</v>
       </c>
-      <c r="G60" s="47"/>
-      <c r="H60" s="48"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="55"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
@@ -4421,17 +5463,17 @@
       <c r="A61" s="8">
         <v>3</v>
       </c>
-      <c r="B61" s="73" t="s">
-        <v>90</v>
+      <c r="B61" s="53" t="s">
+        <v>88</v>
       </c>
-      <c r="C61" s="47"/>
-      <c r="D61" s="47"/>
-      <c r="E61" s="48"/>
-      <c r="F61" s="49">
+      <c r="C61" s="54"/>
+      <c r="D61" s="54"/>
+      <c r="E61" s="55"/>
+      <c r="F61" s="56">
         <v>55</v>
       </c>
-      <c r="G61" s="47"/>
-      <c r="H61" s="48"/>
+      <c r="G61" s="54"/>
+      <c r="H61" s="55"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
@@ -4456,17 +5498,17 @@
       <c r="A62" s="8">
         <v>2</v>
       </c>
-      <c r="B62" s="72" t="s">
+      <c r="B62" s="114" t="s">
         <v>16</v>
       </c>
-      <c r="C62" s="47"/>
-      <c r="D62" s="47"/>
-      <c r="E62" s="48"/>
-      <c r="F62" s="49">
+      <c r="C62" s="54"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="55"/>
+      <c r="F62" s="56">
         <v>50</v>
       </c>
-      <c r="G62" s="47"/>
-      <c r="H62" s="48"/>
+      <c r="G62" s="54"/>
+      <c r="H62" s="55"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
@@ -4491,17 +5533,17 @@
       <c r="A63" s="8">
         <v>1</v>
       </c>
-      <c r="B63" s="46" t="s">
+      <c r="B63" s="115" t="s">
         <v>17</v>
       </c>
-      <c r="C63" s="47"/>
-      <c r="D63" s="47"/>
-      <c r="E63" s="48"/>
-      <c r="F63" s="49">
+      <c r="C63" s="54"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="55"/>
+      <c r="F63" s="56">
         <v>30</v>
       </c>
-      <c r="G63" s="47"/>
-      <c r="H63" s="48"/>
+      <c r="G63" s="54"/>
+      <c r="H63" s="55"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -4593,16 +5635,16 @@
       <c r="D66" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E66" s="50">
+      <c r="E66" s="131">
         <v>1</v>
       </c>
-      <c r="F66" s="50">
+      <c r="F66" s="131">
         <v>0</v>
       </c>
-      <c r="G66" s="52" t="s">
+      <c r="G66" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="H66" s="54" t="s">
+      <c r="H66" s="134" t="s">
         <v>23</v>
       </c>
       <c r="I66" s="1"/>
@@ -4632,10 +5674,10 @@
       <c r="D67" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="E67" s="51"/>
-      <c r="F67" s="51"/>
-      <c r="G67" s="53"/>
-      <c r="H67" s="55"/>
+      <c r="E67" s="132"/>
+      <c r="F67" s="132"/>
+      <c r="G67" s="133"/>
+      <c r="H67" s="135"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
@@ -4657,18 +5699,18 @@
       <c r="AA67" s="1"/>
     </row>
     <row r="68" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="45" t="s">
+      <c r="A68" s="130" t="s">
         <v>39</v>
       </c>
-      <c r="B68" s="45"/>
-      <c r="C68" s="45"/>
-      <c r="D68" s="45"/>
-      <c r="E68" s="45"/>
-      <c r="F68" s="45"/>
-      <c r="G68" s="45"/>
-      <c r="H68" s="45"/>
-      <c r="I68" s="45"/>
-      <c r="J68" s="45"/>
+      <c r="B68" s="130"/>
+      <c r="C68" s="130"/>
+      <c r="D68" s="130"/>
+      <c r="E68" s="130"/>
+      <c r="F68" s="130"/>
+      <c r="G68" s="130"/>
+      <c r="H68" s="130"/>
+      <c r="I68" s="130"/>
+      <c r="J68" s="130"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
@@ -4688,16 +5730,16 @@
       <c r="AA68" s="1"/>
     </row>
     <row r="69" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="45"/>
-      <c r="B69" s="45"/>
-      <c r="C69" s="45"/>
-      <c r="D69" s="45"/>
-      <c r="E69" s="45"/>
-      <c r="F69" s="45"/>
-      <c r="G69" s="45"/>
-      <c r="H69" s="45"/>
-      <c r="I69" s="45"/>
-      <c r="J69" s="45"/>
+      <c r="A69" s="130"/>
+      <c r="B69" s="130"/>
+      <c r="C69" s="130"/>
+      <c r="D69" s="130"/>
+      <c r="E69" s="130"/>
+      <c r="F69" s="130"/>
+      <c r="G69" s="130"/>
+      <c r="H69" s="130"/>
+      <c r="I69" s="130"/>
+      <c r="J69" s="130"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
@@ -30847,36 +31889,58 @@
     </row>
   </sheetData>
   <mergeCells count="116">
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="B42:C43"/>
-    <mergeCell ref="B44:C45"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="F59:H59"/>
-    <mergeCell ref="F58:H58"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:J26"/>
-    <mergeCell ref="B34:C35"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="B36:C37"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="E23:J23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="A68:J69"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="F66:F67"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="H66:H67"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="A34:A45"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="B38:C39"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="B40:C41"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A32:C33"/>
+    <mergeCell ref="D32:F33"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G14:H14"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="G13:H13"/>
@@ -30894,8 +31958,6 @@
     <mergeCell ref="E7:F8"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A3:B4"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="G32:J32"/>
     <mergeCell ref="G5:J5"/>
     <mergeCell ref="G6:J8"/>
     <mergeCell ref="A7:B8"/>
@@ -30903,17 +31965,38 @@
     <mergeCell ref="C7:D8"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="B38:C39"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="B40:C41"/>
-    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D26:J26"/>
+    <mergeCell ref="B34:C35"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="B36:C37"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="E23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="B42:C43"/>
+    <mergeCell ref="B44:C45"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="F59:H59"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="F56:H56"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="F51:H51"/>
     <mergeCell ref="A50:H50"/>
@@ -30922,49 +32005,14 @@
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="B46:C46"/>
     <mergeCell ref="D46:F46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="A34:A45"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A32:C33"/>
-    <mergeCell ref="D32:F33"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="A68:J69"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="F66:F67"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="H66:H67"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G14:H14"/>
   </mergeCells>
-  <phoneticPr fontId="34" type="noConversion"/>
+  <phoneticPr fontId="35" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I11:J11" location="Agrotech!A1" display="Agrotech!A1" xr:uid="{1C8C9087-B7BA-453C-AA01-3B7A2617593C}"/>
+    <hyperlink ref="I12:J12" location="ProjetoEntregas!A1" display="Atividade desafiadora. A partir de um protótipo, codificar a interface de um aplicativo." xr:uid="{8CBA0EFE-77B0-4AFF-A560-06E14C7C1821}"/>
+    <hyperlink ref="I13:J14" location="'Carrinho de compras'!A1" display="Situação de aprendizagem formativa. A partir de um protótipo, codificar a interface de um aplicativo." xr:uid="{340FEED4-31BD-40F7-B9EC-07747F4BE175}"/>
+    <hyperlink ref="I15:J15" location="PapelariaClaroEscuro!A1" display="Atividade desafiadora. A partir de um protótipo, codificar a interface de um aplicativo." xr:uid="{656727CB-6C43-4167-96E3-3AB0127B2E95}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -30978,125 +32026,758 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE6C8CF-909C-4356-A34D-FF630683263A}">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="106.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="41" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="18" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" s="144" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="143" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" s="144" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="145" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="146" t="s">
+    <row r="5" spans="1:1" s="144" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="143" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" s="144" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="146" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" s="144" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="146" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" s="144" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="143" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" s="144" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="143" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" s="144" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="143" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" s="144" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="146" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" s="144" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="143" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" s="144" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="143" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" s="144" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="143" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" s="144" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="143" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" s="144" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="143" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="146" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="143" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A19" s="143" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="147" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="146" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="149" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="39"/>
+    </row>
+    <row r="24" spans="1:1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="147" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="150" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="376.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A22" r:id="rId1" xr:uid="{7F4617BC-E2B8-4CD3-B553-3B404C28B104}"/>
+  </hyperlinks>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCDB802B-C4F8-489B-982C-218EC5113374}">
+  <dimension ref="A1:B54"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="95.625" customWidth="1"/>
+    <col min="2" max="2" width="68.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="23.25" x14ac:dyDescent="0.2">
+      <c r="A1" s="167" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="167"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="168" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="168"/>
+    </row>
+    <row r="3" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="A3" s="169" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="145" t="s">
+      <c r="B3" s="169"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="170" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="170"/>
+    </row>
+    <row r="5" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A5" s="171" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="171"/>
+    </row>
+    <row r="6" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="170" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="172"/>
+    </row>
+    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="173" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" s="173"/>
+    </row>
+    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B8" s="174" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="146"/>
+      <c r="B9" s="174"/>
+    </row>
+    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="146"/>
+      <c r="B10" s="174"/>
+    </row>
+    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="146"/>
+      <c r="B11" s="174"/>
+    </row>
+    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="146"/>
+      <c r="B12" s="174"/>
+    </row>
+    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="146"/>
+      <c r="B13" s="174"/>
+    </row>
+    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="146" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="174"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="143" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="146" t="s">
-        <v>119</v>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="147" t="s">
+        <v>179</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="145" t="s">
-        <v>121</v>
+    <row r="17" spans="1:1" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="147" t="s">
+        <v>180</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="147" t="s">
-        <v>122</v>
+    <row r="23" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="146" t="s">
+        <v>182</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7" s="145" t="s">
-        <v>123</v>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="147" t="s">
+        <v>183</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" s="145" t="s">
-        <v>124</v>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="147" t="s">
+        <v>184</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="145" t="s">
-        <v>125</v>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="147" t="s">
+        <v>185</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="145" t="s">
-        <v>126</v>
+    <row r="27" spans="1:1" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A27" s="147" t="s">
+        <v>186</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" s="145" t="s">
-        <v>127</v>
+    <row r="42" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A42" s="146" t="s">
+        <v>193</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" s="145" t="s">
-        <v>128</v>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A43" s="147" t="s">
+        <v>187</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A13" s="145" t="s">
-        <v>129</v>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" s="147" t="s">
+        <v>188</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14" s="145" t="s">
-        <v>130</v>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" s="147" t="s">
+        <v>189</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A15" s="145" t="s">
-        <v>131</v>
+    <row r="48" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A48" s="146" t="s">
+        <v>192</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A16" s="145" t="s">
-        <v>132</v>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" s="147" t="s">
+        <v>190</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="145" t="s">
-        <v>133</v>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>191</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="145"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="145"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="145"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" s="145"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" s="144" t="s">
-        <v>117</v>
+    <row r="52" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A52" s="150" t="s">
+        <v>194</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" s="144"/>
-    </row>
-    <row r="24" spans="1:1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="144" t="s">
-        <v>118</v>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A53" s="148" t="s">
+        <v>195</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="376.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A54" s="148" t="s">
+        <v>196</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A5:B5"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7557C94-0DB2-416F-BC9B-8194EC81FEB0}">
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="59.125" customWidth="1"/>
+    <col min="2" max="2" width="60.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="176" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="176"/>
+    </row>
+    <row r="2" spans="1:2" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="151" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="152" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="152" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="159" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="153" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="160"/>
+      <c r="B5" s="154" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="161" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6" s="155" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="162"/>
+      <c r="B7" s="156" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="157" t="s">
+        <v>149</v>
+      </c>
+      <c r="B8" s="157" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="158" t="s">
+        <v>200</v>
+      </c>
+      <c r="B9" s="158" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="157" t="s">
+        <v>151</v>
+      </c>
+      <c r="B10" s="157" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="158" t="s">
+        <v>202</v>
+      </c>
+      <c r="B11" s="158" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="157" t="s">
+        <v>153</v>
+      </c>
+      <c r="B12" s="157" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="158" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" s="158" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="157" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" s="157" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="163" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="142" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="142" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="142" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="163" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="151"/>
+    </row>
+    <row r="21" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="151"/>
+    </row>
+    <row r="22" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="151"/>
+    </row>
+    <row r="23" spans="1:1" ht="24.75" x14ac:dyDescent="0.2">
+      <c r="A23" s="163" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="151" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A25" s="164" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="69" x14ac:dyDescent="0.2">
+      <c r="A26" s="142" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A27" s="164" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A28" s="175" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="24.75" x14ac:dyDescent="0.2">
+      <c r="A29" s="163" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A30" s="142" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A31" s="142" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A32" s="142" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A33" s="142" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A34" s="142" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A35" s="142" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A28" r:id="rId1" display="https://github.com/wellifabio/flutter_cart_api_whats_2026/blob/main/app-release.apk" xr:uid="{BBF38514-F32A-4066-9EBA-55804AE47DCB}"/>
+    <hyperlink ref="A1:B1" r:id="rId2" display="Carrinho de compras" xr:uid="{630700B8-BEC4-43B0-95AE-CA9E9462F7C0}"/>
+  </hyperlinks>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E309A475-D0DC-48AC-9FF1-716D0F32E89E}">
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="72.75" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="26.25" x14ac:dyDescent="0.2">
+      <c r="A1" s="166" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="166"/>
+    </row>
+    <row r="2" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="151" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="152" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="152" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="159" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="153" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="160"/>
+      <c r="B5" s="154" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="161" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" s="155" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="162"/>
+      <c r="B7" s="156" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="157" t="s">
+        <v>149</v>
+      </c>
+      <c r="B8" s="157" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="158" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="158" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="157" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" s="157" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="161" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" s="155" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="162"/>
+      <c r="B12" s="156" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="24.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="163" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A14" s="142" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="142" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A16" s="142" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="165" t="s">
+        <v>175</v>
+      </c>
+      <c r="B17" s="165"/>
+    </row>
+    <row r="18" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A18" s="151"/>
+    </row>
+    <row r="19" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A19" s="151"/>
+    </row>
+    <row r="20" spans="1:2" ht="24.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="163" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A21" s="151" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="164" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="69" x14ac:dyDescent="0.2">
+      <c r="A23" s="142" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="164" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="24.75" x14ac:dyDescent="0.2">
+      <c r="A25" s="163" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A26" s="142" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A27" s="142" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A28" s="142" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A29" s="142" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="51.75" x14ac:dyDescent="0.2">
+      <c r="A30" s="142" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A31" s="142" t="s">
+        <v>174</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A17:B17"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:B1" r:id="rId1" display="Exemplo de Listas Cores e Temas" xr:uid="{29D346F7-564E-4A16-9BCC-09F5532E04CC}"/>
+  </hyperlinks>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>